--- a/Data/dim_date.xlsx
+++ b/Data/dim_date.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Machine Learning\Power BI\Projects\3\Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analysis\Power BI\Projects\3- Andalusia\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66830AF-F635-44FD-AA17-4288302C9127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F7CA92-5B50-43EE-A032-6AAAC3FA8807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56350C31-280B-463A-A3AA-DD87B752F566}"/>
   </bookViews>
@@ -39,32 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Date Key</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="80">
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Month Name</t>
-  </si>
-  <si>
-    <t>Quarter</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Day Name</t>
-  </si>
-  <si>
     <t>20250301</t>
   </si>
   <si>
@@ -90,6 +69,216 @@
   </si>
   <si>
     <t>Thursday</t>
+  </si>
+  <si>
+    <t>date_key</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>month_name</t>
+  </si>
+  <si>
+    <t>quarter</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>day_name</t>
+  </si>
+  <si>
+    <t>20250302</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>20250303</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>20250304</t>
+  </si>
+  <si>
+    <t>20250305</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>20250306</t>
+  </si>
+  <si>
+    <t>20250307</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>20250308</t>
+  </si>
+  <si>
+    <t>20250309</t>
+  </si>
+  <si>
+    <t>20250310</t>
+  </si>
+  <si>
+    <t>20250311</t>
+  </si>
+  <si>
+    <t>20250312</t>
+  </si>
+  <si>
+    <t>20250313</t>
+  </si>
+  <si>
+    <t>20250314</t>
+  </si>
+  <si>
+    <t>20250315</t>
+  </si>
+  <si>
+    <t>20250316</t>
+  </si>
+  <si>
+    <t>20250317</t>
+  </si>
+  <si>
+    <t>20250318</t>
+  </si>
+  <si>
+    <t>20250319</t>
+  </si>
+  <si>
+    <t>20250320</t>
+  </si>
+  <si>
+    <t>20250321</t>
+  </si>
+  <si>
+    <t>20250322</t>
+  </si>
+  <si>
+    <t>20250323</t>
+  </si>
+  <si>
+    <t>20250324</t>
+  </si>
+  <si>
+    <t>20250325</t>
+  </si>
+  <si>
+    <t>20250326</t>
+  </si>
+  <si>
+    <t>20250327</t>
+  </si>
+  <si>
+    <t>20250328</t>
+  </si>
+  <si>
+    <t>20250329</t>
+  </si>
+  <si>
+    <t>20250330</t>
+  </si>
+  <si>
+    <t>20250331</t>
+  </si>
+  <si>
+    <t>20250402</t>
+  </si>
+  <si>
+    <t>20250403</t>
+  </si>
+  <si>
+    <t>20250404</t>
+  </si>
+  <si>
+    <t>20250405</t>
+  </si>
+  <si>
+    <t>20250406</t>
+  </si>
+  <si>
+    <t>20250407</t>
+  </si>
+  <si>
+    <t>20250408</t>
+  </si>
+  <si>
+    <t>20250409</t>
+  </si>
+  <si>
+    <t>20250410</t>
+  </si>
+  <si>
+    <t>20250411</t>
+  </si>
+  <si>
+    <t>20250412</t>
+  </si>
+  <si>
+    <t>20250413</t>
+  </si>
+  <si>
+    <t>20250414</t>
+  </si>
+  <si>
+    <t>20250415</t>
+  </si>
+  <si>
+    <t>20250416</t>
+  </si>
+  <si>
+    <t>20250417</t>
+  </si>
+  <si>
+    <t>20250418</t>
+  </si>
+  <si>
+    <t>20250419</t>
+  </si>
+  <si>
+    <t>20250420</t>
+  </si>
+  <si>
+    <t>20250421</t>
+  </si>
+  <si>
+    <t>20250422</t>
+  </si>
+  <si>
+    <t>20250423</t>
+  </si>
+  <si>
+    <t>20250424</t>
+  </si>
+  <si>
+    <t>20250425</t>
+  </si>
+  <si>
+    <t>20250426</t>
+  </si>
+  <si>
+    <t>20250427</t>
+  </si>
+  <si>
+    <t>20250428</t>
+  </si>
+  <si>
+    <t>20250429</t>
+  </si>
+  <si>
+    <t>20250430</t>
   </si>
 </sst>
 </file>
@@ -134,7 +323,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -470,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDB464EF-8FA8-479D-B6C1-4593296893CE}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -478,103 +667,1637 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45717</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45718</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>45719</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45720</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45721</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45722</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>6</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45723</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="H8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>45724</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
         <v>8</v>
       </c>
-      <c r="B2" s="2">
-        <v>45717</v>
-      </c>
-      <c r="C2" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D2" s="3">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="H9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>45725</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3">
         <v>9</v>
       </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45726</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="H11" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>45727</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
         <v>11</v>
       </c>
-      <c r="B3" s="2">
+      <c r="H12" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>45728</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>12</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>45729</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>13</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>45730</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45731</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3">
+        <v>15</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45732</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3">
+        <v>16</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45733</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3">
+        <v>17</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45734</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3">
+        <v>18</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45735</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3">
+        <v>19</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>45736</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>20</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>45737</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>21</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>45738</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D23" s="3">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3">
+        <v>22</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>45739</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>23</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>45740</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D25" s="3">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3">
+        <v>24</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>45741</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D26" s="3">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3">
+        <v>25</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>45742</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D27" s="3">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3">
+        <v>26</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>45743</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D28" s="3">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>27</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>45744</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D29" s="3">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3">
+        <v>28</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>45745</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D30" s="3">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3">
+        <v>29</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>45746</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D31" s="3">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3">
+        <v>30</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>45747</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D32" s="3">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3">
+        <v>31</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>45748</v>
       </c>
-      <c r="C3" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D3" s="3">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D33" s="3">
+        <v>4</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>2</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>45749</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D34" s="3">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="3">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3">
+        <v>2</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>45750</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D35" s="3">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
+        <v>2</v>
+      </c>
+      <c r="G35" s="3">
+        <v>3</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>45751</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D36" s="3">
+        <v>4</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2</v>
+      </c>
+      <c r="G36" s="3">
+        <v>4</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>45752</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D37" s="3">
+        <v>4</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2</v>
+      </c>
+      <c r="G37" s="3">
+        <v>5</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>45753</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D38" s="3">
+        <v>4</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" s="3">
+        <v>2</v>
+      </c>
+      <c r="G38" s="3">
+        <v>6</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>45754</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D39" s="3">
+        <v>4</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="3">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3">
+        <v>7</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>45755</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D40" s="3">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" s="3">
+        <v>2</v>
+      </c>
+      <c r="G40" s="3">
+        <v>8</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>45756</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D41" s="3">
+        <v>4</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2</v>
+      </c>
+      <c r="G41" s="3">
+        <v>9</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>45757</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D42" s="3">
+        <v>4</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2</v>
+      </c>
+      <c r="G42" s="3">
+        <v>10</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>45758</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D43" s="3">
+        <v>4</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2</v>
+      </c>
+      <c r="G43" s="3">
+        <v>11</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>45759</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D44" s="3">
+        <v>4</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3">
+        <v>2</v>
+      </c>
+      <c r="G44" s="3">
         <v>12</v>
       </c>
-      <c r="F3" s="3">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="H44" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>45760</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D45" s="3">
+        <v>4</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2</v>
+      </c>
+      <c r="G45" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="H45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45761</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D46" s="3">
+        <v>4</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2</v>
+      </c>
+      <c r="G46" s="3">
         <v>14</v>
       </c>
-      <c r="B4" s="2">
+      <c r="H46" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>45762</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D47" s="3">
+        <v>4</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2</v>
+      </c>
+      <c r="G47" s="3">
+        <v>15</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>45763</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D48" s="3">
+        <v>4</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
+        <v>2</v>
+      </c>
+      <c r="G48" s="3">
+        <v>16</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>45764</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D49" s="3">
+        <v>4</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2</v>
+      </c>
+      <c r="G49" s="3">
+        <v>17</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>45765</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D50" s="3">
+        <v>4</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="3">
+        <v>2</v>
+      </c>
+      <c r="G50" s="3">
+        <v>18</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>45766</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D51" s="3">
+        <v>4</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" s="3">
+        <v>2</v>
+      </c>
+      <c r="G51" s="3">
+        <v>19</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>45767</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D52" s="3">
+        <v>4</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2</v>
+      </c>
+      <c r="G52" s="3">
+        <v>20</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>45768</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D53" s="3">
+        <v>4</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F53" s="3">
+        <v>2</v>
+      </c>
+      <c r="G53" s="3">
+        <v>21</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>45769</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D54" s="3">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="3">
+        <v>2</v>
+      </c>
+      <c r="G54" s="3">
+        <v>22</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>45770</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D55" s="3">
+        <v>4</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" s="3">
+        <v>2</v>
+      </c>
+      <c r="G55" s="3">
+        <v>23</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>45771</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D56" s="3">
+        <v>4</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" s="3">
+        <v>2</v>
+      </c>
+      <c r="G56" s="3">
+        <v>24</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>45772</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C57" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D57" s="3">
+        <v>4</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2</v>
+      </c>
+      <c r="G57" s="3">
+        <v>25</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>45773</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D58" s="3">
+        <v>4</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3">
+        <v>2</v>
+      </c>
+      <c r="G58" s="3">
+        <v>26</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>45774</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C59" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D59" s="3">
+        <v>4</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2</v>
+      </c>
+      <c r="G59" s="3">
+        <v>27</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>45775</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C60" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D60" s="3">
+        <v>4</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3">
+        <v>2</v>
+      </c>
+      <c r="G60" s="3">
+        <v>28</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>45776</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C61" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D61" s="3">
+        <v>4</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" s="3">
+        <v>2</v>
+      </c>
+      <c r="G61" s="3">
+        <v>29</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>45777</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D62" s="3">
+        <v>4</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
+        <v>2</v>
+      </c>
+      <c r="G62" s="3">
+        <v>30</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
         <v>45778</v>
       </c>
-      <c r="C4" s="3">
-        <v>2025</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D63" s="3">
+        <v>5</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="3">
+        <v>2</v>
+      </c>
+      <c r="G63" s="3">
+        <v>1</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
